--- a/out/Attention-Mamba1_repeat_5_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.354107168743696</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.354107168743696</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.4257236973058409</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.4257236973058409</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC45" t="n">
-        <v>-9.602490218053572e-05</v>
+        <v>-8.092237725213636e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1103141693229315</v>
+        <v>-0.09296426888755301</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1104101942251121</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1104101942251121</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1104101942251121</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1104101942251121</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1104101942251121</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1104101942251121</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1104101942251121</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1104101942251121</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1104101942251121</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1104101942251121</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1104101942251121</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1104101942251121</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1104101942251121</v>
+        <v>-0.09304519126480515</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1104952424562321</v>
+        <v>-0.0932263482319623</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.30581381342533</v>
+        <v>0.6513991970996914</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5017200725936086</v>
+        <v>1.210822756279273</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02178916999913368</v>
+        <v>0.04641201944196855</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2389935992613316</v>
+        <v>0.6512027555875856</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03821078014821919</v>
+        <v>0.08139086854627529</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.293618901749097</v>
+        <v>0.7675571682119979</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0464218970092958</v>
+        <v>0.09888060488496266</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3482480231796743</v>
+        <v>0.8839195083875374</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01228423204539134</v>
+        <v>0.02616612051256925</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3263356521712735</v>
+        <v>0.837245230557583</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.006822865414426962</v>
+        <v>0.01453786049998768</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.327687144883655</v>
+        <v>0.8401285273668692</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01433939093219012</v>
+        <v>0.03054232348667754</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.349550128043744</v>
+        <v>0.8866966476465896</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.005630125573935356</v>
+        <v>0.01199795069058098</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3464597262626148</v>
+        <v>0.8801196689118442</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004007199124413195</v>
+        <v>0.00854205359478391</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3488433770182897</v>
+        <v>0.8852025502228409</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001574227464257427</v>
+        <v>0.003359854390739384</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3479811427261927</v>
+        <v>0.883371827137554</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0008921024631995111</v>
+        <v>0.001904810913924732</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3481888412776813</v>
+        <v>0.883819633847682</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000336741446128381</v>
+        <v>0.0007219345537919857</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3479695045455448</v>
+        <v>0.8833583404617582</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001546392642953449</v>
+        <v>0.0003362977374590134</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3479429002481692</v>
+        <v>0.8833073090954032</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.393474648784013e-05</v>
+        <v>0.000120135420624866</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3478948946783403</v>
+        <v>0.8832109958991909</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.217148705972408e-05</v>
+        <v>3.172790287774317e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3478657241120993</v>
+        <v>0.8831546744156608</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>3.58574352986204e-06</v>
+        <v>1.360244431470109e-05</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3478607107085425</v>
+        <v>0.8831496453746213</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-3.767886923740136e-07</v>
+        <v>4.760112760543749e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.347856401831225</v>
+        <v>0.8831460635797379</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>1.972121134556507e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3478532342096602</v>
+        <v>0.8831447283366085</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.752393347619798e-06</v>
+        <v>-1.880983369049493e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3478478648826724</v>
+        <v>0.883138988761598</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.70653621650487e-06</v>
+        <v>-4.413072433009741e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3478418721492421</v>
+        <v>0.883132334031164</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3478365043606637</v>
+        <v>0.8831267825001264</v>
       </c>
     </row>
     <row r="81">
@@ -65328,7 +65328,7 @@
         <v>0</v>
       </c>
       <c r="IY81" t="n">
-        <v>0</v>
+        <v>-4.853353791035969e-06</v>
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3478365411091554</v>
+        <v>0.8831218556493516</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3478366513546309</v>
+        <v>0.8831219658948272</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3478367248516145</v>
+        <v>0.8831220393918108</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3478369085940737</v>
+        <v>0.8831222231342699</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3478384520307302</v>
+        <v>0.8831237665709264</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3478399219704033</v>
+        <v>0.8831252365105995</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3478411714191253</v>
+        <v>0.8831264859593215</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1742763026941591</v>
+        <v>3.954107168743695</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3478425311133226</v>
+        <v>0.8831278456535188</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-15.88973846592426</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3478403262038133</v>
+        <v>0.8831256407440096</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.2363827036687994</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3478399219704033</v>
+        <v>0.8831252365105995</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3478390767550913</v>
+        <v>0.8831243912952875</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3478396279824686</v>
+        <v>0.8831249425226648</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3478392972460422</v>
+        <v>0.8831246117862384</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3478390032581077</v>
+        <v>0.8831243177983039</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3478390767550913</v>
+        <v>0.8831243912952875</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3478386357731894</v>
+        <v>0.8831239503133855</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3478385255277138</v>
+        <v>0.88312384006791</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.4257236973058409</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3478384887792221</v>
+        <v>0.8831238033194183</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3478386357731894</v>
+        <v>0.8831239503133855</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3478381580427957</v>
+        <v>0.883123472582992</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.347839113503583</v>
+        <v>0.8831244280437792</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3478390767550913</v>
+        <v>0.8831243912952875</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3478387460186649</v>
+        <v>0.8831240605588612</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3478391870005669</v>
+        <v>0.8831245015407631</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3478385622762057</v>
+        <v>0.8831238768164019</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3478383785337466</v>
+        <v>0.8831236930739428</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3478379743003366</v>
+        <v>0.8831232888405328</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3478371290850246</v>
+        <v>0.8831224436252207</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3478370923365329</v>
+        <v>0.883122406876729</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3478372393305001</v>
+        <v>0.8831225538706964</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3478371658335165</v>
+        <v>0.8831224803737128</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3478372393305001</v>
+        <v>0.8831225538706964</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3478372760789921</v>
+        <v>0.8831225906191883</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3478371658335165</v>
+        <v>0.8831224803737128</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3478376068154185</v>
+        <v>0.8831229213556147</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3478374965699429</v>
+        <v>0.8831228111101391</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.347837459821451</v>
+        <v>0.8831227743616472</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3478373863244674</v>
+        <v>0.8831227008646636</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3478373495759757</v>
+        <v>0.8831226641161719</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3478371290850246</v>
+        <v>0.8831224436252207</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.347837055588041</v>
+        <v>0.8831223701282371</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3478369820910573</v>
+        <v>0.8831222966312535</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3478370188395493</v>
+        <v>0.8831223333797454</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3478369085940737</v>
+        <v>0.8831222231342699</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3478370188395493</v>
+        <v>0.8831223333797454</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.8363827036687994</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3478373128274838</v>
+        <v>0.88312262736768</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_5_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC45" t="n">
-        <v>-9.602490218053572e-05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1103141693229315</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1104101942251121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1104101942251121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1104101942251121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -39892,17 +39892,17 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1104101942251121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -40687,17 +40687,17 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1104101942251121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -41482,17 +41482,17 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1104101942251121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -42277,17 +42277,17 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1104101942251121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -43072,17 +43072,17 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1104101942251121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1104101942251121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -44662,17 +44662,17 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1104101942251121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -45457,17 +45457,17 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1104101942251121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -46252,17 +46252,17 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1104101942251121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -47047,17 +47047,17 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1104101942251121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -47842,17 +47842,17 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1104952424562321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.30581381342533</v>
+        <v>0</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5017200725936086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02178916999913368</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2389935992613316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03821078014821919</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.293618901749097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0464218970092958</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.3482480231796743</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01228423204539134</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3263356521712735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.006822865414426962</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.327687144883655</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01433939093219012</v>
+        <v>0</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.349550128043744</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.005630125573935356</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3464597262626148</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004007199124413195</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3488433770182897</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001574227464257427</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3479811427261927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -56583,21 +56583,21 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0008921024631995111</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3481888412776813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -57378,21 +57378,21 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000336741446128381</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3479695045455448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -58173,21 +58173,21 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001546392642953449</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3479429002481692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -58968,21 +58968,21 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>5.393474648784013e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3478948946783403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -59763,21 +59763,21 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.217148705972408e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3478657241120993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -60558,21 +60558,21 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>3.58574352986204e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3478607107085425</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -61353,21 +61353,21 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-3.767886923740136e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.347856401831225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -62148,21 +62148,21 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.513939432721747e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3478532342096602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -62943,21 +62943,21 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.752393347619798e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3478478648826724</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -63738,21 +63738,21 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.70653621650487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3478418721492421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-4.890058184668745e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3478365043606637</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3478365411091554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3478366513546309</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.3478367248516145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3478369085940737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3478384520307302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3478399219704033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3478411714191253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.9425263098030442</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3478425311133226</v>
+        <v>-7.234960775531363e-05</v>
       </c>
     </row>
     <row r="89">
@@ -71688,21 +71688,21 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>0</v>
+        <v>-0.05094636545097517</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-15.88973846592426</v>
+        <v>-0.9425263098030442</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3478403262038133</v>
+        <v>-0.05101871505873045</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.1742763026941591</v>
+        <v>-0.9425263098030442</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3478399219704033</v>
+        <v>-0.05108708843983523</v>
       </c>
     </row>
     <row r="91">
@@ -73278,21 +73278,21 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>0</v>
+        <v>-0.03164553989703889</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3478390767550913</v>
+        <v>-0.08273262833687407</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.3478396279824686</v>
+        <v>-0.08273262833687407</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA93" t="n">
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3478392972460422</v>
+        <v>-0.08283116282711248</v>
       </c>
     </row>
     <row r="94">
@@ -75663,21 +75663,21 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>0</v>
+        <v>-0.01928779776227677</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.3478390032581077</v>
+        <v>-0.1021189605893893</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3478390767550913</v>
+        <v>-0.1022154848385657</v>
       </c>
     </row>
     <row r="96">
@@ -77253,21 +77253,21 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>0</v>
+        <v>-0.03037446606050734</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA96" t="n">
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3478386357731894</v>
+        <v>-0.1325899508990731</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3478385255277138</v>
+        <v>-0.1326832665777855</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA98" t="n">
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.4257236973058409</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3478384887792221</v>
+        <v>-0.1357044781039786</v>
       </c>
     </row>
     <row r="99">
@@ -79638,21 +79638,21 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>0</v>
+        <v>0.0004256908308718278</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.2462105352954338</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3478386357731894</v>
+        <v>-0.1234992370786529</v>
       </c>
     </row>
     <row r="100">
@@ -80433,21 +80433,21 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>0</v>
+        <v>-0.02927539607622745</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA100" t="n">
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3478381580427957</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.347839113503583</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3478390767550913</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3478387460186649</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3478391870005669</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3478385622762057</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.3478383785337466</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3478379743003366</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.3478371290850246</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3478370923365329</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3478372393305001</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3478371658335165</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3478372393305001</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3478372760789921</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3478371658335165</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3478376068154185</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3478374965699429</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.347837459821451</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3478373863244674</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.3478373495759757</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.3478371290850246</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.347837055588041</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3478369820910573</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3478370188395493</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3478369085940737</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>TakeProfit</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3478370188395493</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.082561524747701e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell (Force)</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.1742763026941591</v>
+        <v>0.04621053529543377</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3478373128274838</v>
+        <v>-0.1615384551163745</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_5_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.009926311671733856</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.3000000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.01221140474081039</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.16</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01651187613606453</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.2462105352954338</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.01883790642023087</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.2462105352954338</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.01244232058525085</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.2462105352954338</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.01088684052228928</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.2462105352954338</v>
+        <v>0.16</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.01049964874982834</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.009029723703861237</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.009653113782405853</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.009071022272109985</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.009909629821777344</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.009309589862823486</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.009590893983840942</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.009323835372924805</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.01133135706186295</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.009390875697135925</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.008906938135623932</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.008619949221611023</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.008729636669158936</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.008651316165924072</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.00823529064655304</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.008725717663764954</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.008505389094352722</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.009477332234382629</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.008551701903343201</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.008857503533363342</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.008396796882152557</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.008702360093593597</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.009014599025249481</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.009419336915016174</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01462959870696068</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.01002238690853119</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.0105571523308754</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.01008246093988419</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.008982233703136444</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0103568509221077</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.009068213403224945</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.009024001657962799</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.01102948188781738</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.01141675561666489</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.01127377897500992</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.01311427727341652</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01730822399258614</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.01783081889152527</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>-0.0001196160965063609</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.1374159204966616</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.01057562232017517</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.01436848193407059</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.01039642840623856</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="49">
@@ -39892,17 +39892,17 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.01147066056728363</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.3</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="50">
@@ -40687,17 +40687,17 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01025357097387314</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="51">
@@ -41482,17 +41482,17 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.0104639008641243</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="52">
@@ -42277,17 +42277,17 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.01002160459756851</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="53">
@@ -43072,17 +43072,17 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.01154611259698868</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.3</v>
       </c>
       <c r="JC53" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="54">
@@ -43867,17 +43867,17 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.0108155757188797</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="55">
@@ -44662,17 +44662,17 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.01126282662153244</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="56">
@@ -45457,17 +45457,17 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01088502258062363</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="57">
@@ -46252,17 +46252,17 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.0109432190656662</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="58">
@@ -47047,17 +47047,17 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.01185174286365509</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0</v>
+        <v>-0.1375355365931678</v>
       </c>
     </row>
     <row r="59">
@@ -47842,17 +47842,17 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01538984850049019</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0</v>
+        <v>-0.1376374470532828</v>
       </c>
     </row>
     <row r="60">
@@ -48633,21 +48633,21 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0</v>
+        <v>0.3664465486768422</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.0111919566988945</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0</v>
+        <v>0.5959597555715596</v>
       </c>
     </row>
     <row r="61">
@@ -49428,21 +49428,21 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>0.02610927624186771</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.01259717345237732</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0</v>
+        <v>0.2811434245759987</v>
       </c>
     </row>
     <row r="62">
@@ -50223,21 +50223,21 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>0.04578677454656582</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01489774882793427</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0</v>
+        <v>0.3465989841554928</v>
       </c>
     </row>
     <row r="63">
@@ -51018,21 +51018,21 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>0.05562521191238126</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.01152514666318893</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0</v>
+        <v>0.4120589009465191</v>
       </c>
     </row>
     <row r="64">
@@ -51813,21 +51813,21 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0</v>
+        <v>0.01471982477267596</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.00995270162820816</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC64" t="n">
-        <v>0</v>
+        <v>0.3858020259240663</v>
       </c>
     </row>
     <row r="65">
@@ -52608,21 +52608,21 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>0.00817662520053386</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.01787661015987396</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.16</v>
       </c>
       <c r="JC65" t="n">
-        <v>0</v>
+        <v>0.3874224629439409</v>
       </c>
     </row>
     <row r="66">
@@ -53403,21 +53403,21 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0</v>
+        <v>0.01718265724231579</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01752107217907906</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0</v>
+        <v>0.4136203336972494</v>
       </c>
     </row>
     <row r="67">
@@ -54198,21 +54198,21 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0</v>
+        <v>0.006746735455553322</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01482636108994484</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>0</v>
+        <v>0.4099182234788127</v>
       </c>
     </row>
     <row r="68">
@@ -54993,21 +54993,21 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>0.004804119156863278</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.01087363809347153</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0</v>
+        <v>0.4127757015268302</v>
       </c>
     </row>
     <row r="69">
@@ -55788,21 +55788,21 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>0.001887900331190759</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01257897168397903</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0</v>
+        <v>0.411743640194752</v>
       </c>
     </row>
     <row r="70">
@@ -56583,21 +56583,21 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>0.0010693649774056</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.01034992188215256</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0</v>
+        <v>0.4119933668105383</v>
       </c>
     </row>
     <row r="71">
@@ -57378,21 +57378,21 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0</v>
+        <v>0.0004036804922772392</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.01011387258768082</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0</v>
+        <v>0.4117316791098689</v>
       </c>
     </row>
     <row r="72">
@@ -58173,21 +58173,21 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0</v>
+        <v>0.000186567117154414</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.009090527892112732</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0</v>
+        <v>0.4117007686524149</v>
       </c>
     </row>
     <row r="73">
@@ -58968,21 +58968,21 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>0</v>
+        <v>6.523730060879578e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.009556762874126434</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0</v>
+        <v>0.4116442214511223</v>
       </c>
     </row>
     <row r="74">
@@ -59763,21 +59763,21 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>0</v>
+        <v>1.59873730729961e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.01021895557641983</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0</v>
+        <v>0.4116100838813491</v>
       </c>
     </row>
     <row r="75">
@@ -60558,21 +60558,21 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>0</v>
+        <v>5.49368653649805e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.009994238615036011</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0</v>
+        <v>0.4116050674992241</v>
       </c>
     </row>
     <row r="76">
@@ -61353,21 +61353,21 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>0</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.01079600304365158</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0</v>
+        <v>0.4116008672899017</v>
       </c>
     </row>
     <row r="77">
@@ -62148,21 +62148,21 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>0</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.009112633764743805</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0</v>
+        <v>0.4115978834107961</v>
       </c>
     </row>
     <row r="78">
@@ -62943,21 +62943,21 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>0</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.008950948715209961</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0</v>
+        <v>0.4115924396657897</v>
       </c>
     </row>
     <row r="79">
@@ -63738,21 +63738,21 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>0</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.009473532438278198</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0</v>
+        <v>0.4115864469323594</v>
       </c>
     </row>
     <row r="80">
@@ -64533,21 +64533,21 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.009980887174606323</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0</v>
+        <v>0.411581079143781</v>
       </c>
     </row>
     <row r="81">
@@ -65332,17 +65332,17 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.01025346666574478</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0</v>
+        <v>0.4115811158922727</v>
       </c>
     </row>
     <row r="82">
@@ -66127,17 +66127,17 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.01026791334152222</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0</v>
+        <v>0.4115812261377482</v>
       </c>
     </row>
     <row r="83">
@@ -66922,17 +66922,17 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.009645707905292511</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
-        <v>0</v>
+        <v>0.4115812996347318</v>
       </c>
     </row>
     <row r="84">
@@ -67717,17 +67717,17 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.01174019277095795</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
-        <v>0</v>
+        <v>0.411581483377191</v>
       </c>
     </row>
     <row r="85">
@@ -68512,17 +68512,17 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01734503731131554</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC85" t="n">
-        <v>0</v>
+        <v>0.4115830268138475</v>
       </c>
     </row>
     <row r="86">
@@ -69307,17 +69307,17 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.0101684033870697</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0</v>
+        <v>0.4115844967535205</v>
       </c>
     </row>
     <row r="87">
@@ -70102,17 +70102,17 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.003047026693820953</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>0</v>
+        <v>0.4115857462022426</v>
       </c>
     </row>
     <row r="88">
@@ -70897,17 +70897,17 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.08056652545928955</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.9425263098030442</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
-        <v>-7.234960775531363e-05</v>
+        <v>0.4115871058964399</v>
       </c>
     </row>
     <row r="89">
@@ -71688,21 +71688,21 @@
         <v>0</v>
       </c>
       <c r="IY89" t="n">
-        <v>-0.05094636545097517</v>
+        <v>0</v>
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.009330570697784424</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9425263098030442</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
-        <v>-0.05101871505873045</v>
+        <v>0.4115849009869306</v>
       </c>
     </row>
     <row r="90">
@@ -72487,17 +72487,17 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01183943450450897</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9425263098030442</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>-0.05108708843983523</v>
+        <v>0.4115844967535205</v>
       </c>
     </row>
     <row r="91">
@@ -73278,21 +73278,21 @@
         <v>0</v>
       </c>
       <c r="IY91" t="n">
-        <v>-0.03164553989703889</v>
+        <v>0</v>
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.006143324077129364</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>-0.08273262833687407</v>
+        <v>0.4115836515382086</v>
       </c>
     </row>
     <row r="92">
@@ -74077,17 +74077,17 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.008977495133876801</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>-0.08273262833687407</v>
+        <v>0.4115842027655858</v>
       </c>
     </row>
     <row r="93">
@@ -74872,17 +74872,17 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.008109919726848602</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>-0.08283116282711248</v>
+        <v>0.4115838720291595</v>
       </c>
     </row>
     <row r="94">
@@ -75663,21 +75663,21 @@
         <v>0</v>
       </c>
       <c r="IY94" t="n">
-        <v>-0.01928779776227677</v>
+        <v>0</v>
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.009585432708263397</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>-0.1021189605893893</v>
+        <v>0.411583578041225</v>
       </c>
     </row>
     <row r="95">
@@ -76462,17 +76462,17 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.009000882506370544</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>-0.1022154848385657</v>
+        <v>0.4115836515382086</v>
       </c>
     </row>
     <row r="96">
@@ -77253,21 +77253,21 @@
         <v>0</v>
       </c>
       <c r="IY96" t="n">
-        <v>-0.03037446606050734</v>
+        <v>0</v>
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.0086497962474823</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>-0.1325899508990731</v>
+        <v>0.4115832105563066</v>
       </c>
     </row>
     <row r="97">
@@ -78052,17 +78052,17 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.008718915283679962</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>-0.1326832665777855</v>
+        <v>0.4115831003108311</v>
       </c>
     </row>
     <row r="98">
@@ -78847,17 +78847,17 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.00939786434173584</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.2462105352954338</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>-0.1357044781039786</v>
+        <v>0.4115830635623394</v>
       </c>
     </row>
     <row r="99">
@@ -79638,21 +79638,21 @@
         <v>0</v>
       </c>
       <c r="IY99" t="n">
-        <v>0.0004256908308718278</v>
+        <v>0</v>
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.008443541824817657</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.2462105352954338</v>
+        <v>0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>-0.1234992370786529</v>
+        <v>0.4115832105563066</v>
       </c>
     </row>
     <row r="100">
@@ -80433,21 +80433,21 @@
         <v>0</v>
       </c>
       <c r="IY100" t="n">
-        <v>-0.02927539607622745</v>
+        <v>0</v>
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.01658894866704941</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC100" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.411582732825913</v>
       </c>
     </row>
     <row r="101">
@@ -81232,17 +81232,17 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.01983602344989777</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115836882867003</v>
       </c>
     </row>
     <row r="102">
@@ -82027,17 +82027,17 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.008576191961765289</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115836515382086</v>
       </c>
     </row>
     <row r="103">
@@ -82822,17 +82822,17 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.008774928748607635</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115833208017822</v>
       </c>
     </row>
     <row r="104">
@@ -83617,17 +83617,17 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.008562035858631134</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115837617836842</v>
       </c>
     </row>
     <row r="105">
@@ -84412,17 +84412,17 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.008691653609275818</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.411583137059323</v>
       </c>
     </row>
     <row r="106">
@@ -85207,17 +85207,17 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.009129226207733154</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115829533168638</v>
       </c>
     </row>
     <row r="107">
@@ -86002,17 +86002,17 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.009170442819595337</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115825490834538</v>
       </c>
     </row>
     <row r="108">
@@ -86797,17 +86797,17 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.009461142122745514</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115817038681419</v>
       </c>
     </row>
     <row r="109">
@@ -87592,17 +87592,17 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.01002740859985352</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115816671196502</v>
       </c>
     </row>
     <row r="110">
@@ -88387,17 +88387,17 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.009944379329681396</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.16</v>
       </c>
       <c r="JC110" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115818141136174</v>
       </c>
     </row>
     <row r="111">
@@ -89182,17 +89182,17 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.009363271296024323</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115817406166338</v>
       </c>
     </row>
     <row r="112">
@@ -89977,17 +89977,17 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.01344960927963257</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115818141136174</v>
       </c>
     </row>
     <row r="113">
@@ -90772,17 +90772,17 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.009066939353942871</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115818508621094</v>
       </c>
     </row>
     <row r="114">
@@ -91567,17 +91567,17 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.01193284243345261</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115817406166338</v>
       </c>
     </row>
     <row r="115">
@@ -92362,17 +92362,17 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.008892253041267395</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115821815985357</v>
       </c>
     </row>
     <row r="116">
@@ -93157,17 +93157,17 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.009403258562088013</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115820713530602</v>
       </c>
     </row>
     <row r="117">
@@ -93952,17 +93952,17 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.008275344967842102</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115820346045683</v>
       </c>
     </row>
     <row r="118">
@@ -94747,17 +94747,17 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.008682504296302795</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115819611075847</v>
       </c>
     </row>
     <row r="119">
@@ -95542,17 +95542,17 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.008342817425727844</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.411581924359093</v>
       </c>
     </row>
     <row r="120">
@@ -96337,17 +96337,17 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.007961072027683258</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115817038681419</v>
       </c>
     </row>
     <row r="121">
@@ -97132,17 +97132,17 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.009019374847412109</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115816303711582</v>
       </c>
     </row>
     <row r="122">
@@ -97927,17 +97927,17 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.008689425885677338</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115815568741746</v>
       </c>
     </row>
     <row r="123">
@@ -98722,17 +98722,17 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.008188396692276001</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.04621053529543377</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115815936226666</v>
       </c>
     </row>
     <row r="124">
@@ -99517,17 +99517,17 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.009391315281391144</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.411581483377191</v>
       </c>
     </row>
     <row r="125">
@@ -100312,17 +100312,17 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.01154385507106781</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.04621053529543377</v>
+        <v>0.5800000000000005</v>
       </c>
       <c r="JC125" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.4115815936226666</v>
       </c>
     </row>
     <row r="126">
@@ -101103,21 +101103,21 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>0</v>
+        <v>-4.082561524747701e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell (Force)</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.01153384149074554</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.04621053529543377</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>-0.1615384551163745</v>
+        <v>0.411581887610601</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-Mamba1_repeat_5_000008.xlsx
+++ b/out/Attention-Mamba1_repeat_5_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.009926311671733856</v>
+        <v>0.009926304221153259</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.3000000000000001</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.01883790642023087</v>
+        <v>0.01883791014552116</v>
       </c>
       <c r="JB5" t="n">
         <v>0.7199999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.01244232058525085</v>
+        <v>0.01244232803583145</v>
       </c>
       <c r="JB6" t="n">
         <v>0.4399999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.01049964874982834</v>
+        <v>0.01049964129924774</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.7199999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.009029723703861237</v>
+        <v>0.00902971625328064</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.8599999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.009653113782405853</v>
+        <v>0.009653098881244659</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.009071022272109985</v>
+        <v>0.009071037173271179</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.009909629821777344</v>
+        <v>0.009909659624099731</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.009590893983840942</v>
+        <v>0.009590901434421539</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.8599999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.009323835372924805</v>
+        <v>0.009323827922344208</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.8599999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.01133135706186295</v>
+        <v>0.01133136451244354</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.8599999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.008729636669158936</v>
+        <v>0.008729606866836548</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.9999999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.00823529064655304</v>
+        <v>0.008235268294811249</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.9999999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.008725717663764954</v>
+        <v>0.008725732564926147</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.9999999999999998</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.008505389094352722</v>
+        <v>0.008505396544933319</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.9999999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.008551701903343201</v>
+        <v>0.008551709353923798</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.9999999999999998</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.008396796882152557</v>
+        <v>0.00839678943157196</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.9999999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.008702360093593597</v>
+        <v>0.008702367544174194</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.009014599025249481</v>
+        <v>0.009014621376991272</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.1199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.009419336915016174</v>
+        <v>0.00941932201385498</v>
       </c>
       <c r="JB31" t="n">
         <v>0.02000000000000007</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.01462959870696068</v>
+        <v>0.01462958380579948</v>
       </c>
       <c r="JB32" t="n">
         <v>0.3</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.0105571523308754</v>
+        <v>0.0105571448802948</v>
       </c>
       <c r="JB34" t="n">
         <v>0.5799999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.01008246093988419</v>
+        <v>0.01008244603872299</v>
       </c>
       <c r="JB35" t="n">
         <v>0.4399999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.008982233703136444</v>
+        <v>0.008982256054878235</v>
       </c>
       <c r="JB36" t="n">
         <v>0.3</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.009068213403224945</v>
+        <v>0.009068220853805542</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.5799999999999998</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.01102948188781738</v>
+        <v>0.01102946698665619</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.16</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.01141675561666489</v>
+        <v>0.01141677051782608</v>
       </c>
       <c r="JB41" t="n">
         <v>0.7199999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.01127377897500992</v>
+        <v>0.01127376407384872</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.01311427727341652</v>
+        <v>0.01311428472399712</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.01783081889152527</v>
+        <v>0.01783084124326706</v>
       </c>
       <c r="JB45" t="n">
         <v>0.8599999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.01436848193407059</v>
+        <v>0.01436848938465118</v>
       </c>
       <c r="JB47" t="n">
         <v>0.5799999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.01039642840623856</v>
+        <v>0.01039644330739975</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.3</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.01147066056728363</v>
+        <v>0.01147063821554184</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.3</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.0104639008641243</v>
+        <v>0.0104639083147049</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.4399999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.01002160459756851</v>
+        <v>0.01002158224582672</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.4399999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.01154611259698868</v>
+        <v>0.01154609769582748</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.3</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.01126282662153244</v>
+        <v>0.01126281917095184</v>
       </c>
       <c r="JB55" t="n">
         <v>0.4399999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.01088502258062363</v>
+        <v>0.01088501513004303</v>
       </c>
       <c r="JB56" t="n">
         <v>0.4399999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.0109432190656662</v>
+        <v>0.010943204164505</v>
       </c>
       <c r="JB57" t="n">
         <v>0.5799999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.01185174286365509</v>
+        <v>0.0118517279624939</v>
       </c>
       <c r="JB58" t="n">
         <v>0.5799999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.01538984850049019</v>
+        <v>0.01538987457752228</v>
       </c>
       <c r="JB59" t="n">
         <v>0.7199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.01259717345237732</v>
+        <v>0.01259716972708702</v>
       </c>
       <c r="JB61" t="n">
         <v>0.7199999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.01489774882793427</v>
+        <v>0.01489773020148277</v>
       </c>
       <c r="JB62" t="n">
         <v>0.4399999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.01152514666318893</v>
+        <v>0.01152513176202774</v>
       </c>
       <c r="JB63" t="n">
         <v>0.5799999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.00995270162820816</v>
+        <v>0.009952671825885773</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.02000000000000007</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.01787661015987396</v>
+        <v>0.01787661388516426</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.16</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.01752107217907906</v>
+        <v>0.01752108335494995</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.3</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.01482636108994484</v>
+        <v>0.01482636481523514</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.16</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.01087363809347153</v>
+        <v>0.01087361574172974</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.4399999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.01034992188215256</v>
+        <v>0.01034993678331375</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.8599999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.01011387258768082</v>
+        <v>0.01011389493942261</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.8599999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.009090527892112732</v>
+        <v>0.009090520441532135</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.009556762874126434</v>
+        <v>0.009556755423545837</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.01021895557641983</v>
+        <v>0.01021894812583923</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.009994238615036011</v>
+        <v>0.009994253516197205</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.01079600304365158</v>
+        <v>0.01079598069190979</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.009112633764743805</v>
+        <v>0.009112641215324402</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.008950948715209961</v>
+        <v>0.008950941264629364</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.009473532438278198</v>
+        <v>0.009473539888858795</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.01025346666574478</v>
+        <v>0.01025345176458359</v>
       </c>
       <c r="JB81" t="n">
         <v>-0.9999999999999998</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.01026791334152222</v>
+        <v>0.01026792079210281</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.2599999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.009645707905292511</v>
+        <v>0.009645715355873108</v>
       </c>
       <c r="JB83" t="n">
         <v>0.02000000000000007</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.01174019277095795</v>
+        <v>0.01174017041921616</v>
       </c>
       <c r="JB84" t="n">
         <v>0.02000000000000007</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.01734503731131554</v>
+        <v>0.01734505966305733</v>
       </c>
       <c r="JB85" t="n">
         <v>0.02000000000000007</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.0101684033870697</v>
+        <v>0.0101684182882309</v>
       </c>
       <c r="JB86" t="n">
         <v>0.3</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.003047026693820953</v>
+        <v>0.00304703414440155</v>
       </c>
       <c r="JB87" t="n">
         <v>0.16</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.08056652545928955</v>
+        <v>0.08056655526161194</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>0.4115871058964399</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.009330570697784424</v>
+        <v>-0.009330525994300842</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0.4115849009869306</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.01183943450450897</v>
+        <v>0.01183944940567017</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0.4115844967535205</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.006143324077129364</v>
+        <v>0.006143331527709961</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0.4115836515382086</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.008977495133876801</v>
+        <v>0.008977457880973816</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0.4115842027655858</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.008109919726848602</v>
+        <v>0.008109927177429199</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.009585432708263397</v>
+        <v>0.009585410356521606</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.0086497962474823</v>
+        <v>0.008649781346321106</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.008718915283679962</v>
+        <v>0.008718922734260559</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.9999999999999998</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.00939786434173584</v>
+        <v>0.009397812187671661</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0.4115830635623394</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.008443541824817657</v>
+        <v>0.008443556725978851</v>
       </c>
       <c r="JB99" t="n">
         <v>0.16</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.01658894866704941</v>
+        <v>0.01658895611763</v>
       </c>
       <c r="JB100" t="n">
         <v>0.1600000000000001</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.01983602344989777</v>
+        <v>0.01983600854873657</v>
       </c>
       <c r="JB101" t="n">
         <v>0.1600000000000001</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.008576191961765289</v>
+        <v>0.008576169610023499</v>
       </c>
       <c r="JB102" t="n">
         <v>0.16</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.008774928748607635</v>
+        <v>0.008774951100349426</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.1199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.008562035858631134</v>
+        <v>0.008562058210372925</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.008691653609275818</v>
+        <v>0.008691608905792236</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.009129226207733154</v>
+        <v>0.009129233658313751</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86009,7 +86009,7 @@
         <v>0.009170442819595337</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0.4115825490834538</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.009461142122745514</v>
+        <v>0.009461112320423126</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0.4115817038681419</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.01002740859985352</v>
+        <v>0.01002737879753113</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
         <v>0.4115816671196502</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.009944379329681396</v>
+        <v>0.009944356977939606</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.16</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0.4115818141136174</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.009363271296024323</v>
+        <v>0.009363286197185516</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.16</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
         <v>0.4115817406166338</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.01344960927963257</v>
+        <v>0.01344960555434227</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.3</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC112" t="n">
         <v>0.4115818141136174</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.009066939353942871</v>
+        <v>0.009066924452781677</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.16</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC113" t="n">
         <v>0.4115818508621094</v>
@@ -91574,7 +91574,7 @@
         <v>0.01193284243345261</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.1600000000000001</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC114" t="n">
         <v>0.4115817406166338</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.008892253041267395</v>
+        <v>0.008892230689525604</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.1199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC115" t="n">
         <v>0.4115821815985357</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.009403258562088013</v>
+        <v>0.009403273463249207</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC116" t="n">
         <v>0.4115820713530602</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.008682504296302795</v>
+        <v>0.008682496845722198</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.9999999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.008342817425727844</v>
+        <v>0.008342824876308441</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.9999999999999998</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.007961072027683258</v>
+        <v>0.007961064577102661</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.9999999999999998</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.009019374847412109</v>
+        <v>0.009019382297992706</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.9999999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.008689425885677338</v>
+        <v>0.008689433336257935</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.9999999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.008188396692276001</v>
+        <v>0.00818837434053421</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.7199999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.009391315281391144</v>
+        <v>0.00939130038022995</v>
       </c>
       <c r="JB124" t="n">
         <v>0.16</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.01154385507106781</v>
+        <v>0.01154386252164841</v>
       </c>
       <c r="JB125" t="n">
         <v>0.5800000000000005</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.01153384149074554</v>
+        <v>0.01153383404016495</v>
       </c>
       <c r="JB126" t="n">
         <v>1.000000000000001</v>
